--- a/data/trans_dic/MCS12_SP_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,1; 29,85</t>
+          <t>24,07; 29,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,83; 32,93</t>
+          <t>26,92; 32,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,86; 29,26</t>
+          <t>22,98; 29,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 31,21</t>
+          <t>24,16; 31,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,32; 35,37</t>
+          <t>30,19; 35,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,87; 42,52</t>
+          <t>37,1; 42,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,33; 41,91</t>
+          <t>35,39; 42,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,58; 42,49</t>
+          <t>36,84; 42,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,38; 32,25</t>
+          <t>28,33; 32,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,66; 37,91</t>
+          <t>33,49; 37,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,06; 35,63</t>
+          <t>31,14; 35,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 37,13</t>
+          <t>32,25; 36,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 16,48</t>
+          <t>13,03; 16,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 22,82</t>
+          <t>19,02; 22,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,49; 18,82</t>
+          <t>15,66; 18,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 18,51</t>
+          <t>11,06; 18,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 24,85</t>
+          <t>20,93; 25,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,07; 32,47</t>
+          <t>28,01; 32,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,77; 24,54</t>
+          <t>20,94; 24,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,32; 49,71</t>
+          <t>22,56; 49,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 20,0</t>
+          <t>17,17; 19,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,7; 26,6</t>
+          <t>23,76; 26,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,2</t>
+          <t>18,62; 21,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,32; 35,18</t>
+          <t>18,63; 36,86</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,4</t>
+          <t>12,41; 18,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 16,37</t>
+          <t>9,85; 16,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,82</t>
+          <t>12,53; 19,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 23,92</t>
+          <t>16,4; 24,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,86; 25,48</t>
+          <t>18,33; 25,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 25,22</t>
+          <t>17,04; 24,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 23,28</t>
+          <t>16,84; 23,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,1; 26,8</t>
+          <t>20,67; 26,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,02; 21,07</t>
+          <t>15,73; 20,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 19,48</t>
+          <t>14,04; 19,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,34</t>
+          <t>15,49; 20,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 24,07</t>
+          <t>19,29; 24,12</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 20,03</t>
+          <t>17,4; 20,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 23,82</t>
+          <t>20,87; 23,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 20,24</t>
+          <t>17,46; 20,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,31</t>
+          <t>14,63; 20,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,9; 28,14</t>
+          <t>25,04; 28,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,06; 34,22</t>
+          <t>31,17; 34,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,32; 28,22</t>
+          <t>25,31; 28,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,3; 47,02</t>
+          <t>26,47; 43,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,73</t>
+          <t>21,74; 23,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,31; 28,67</t>
+          <t>26,54; 28,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,86; 24,0</t>
+          <t>21,86; 23,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,93; 32,53</t>
+          <t>21,83; 34,03</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>248599; 307953</t>
+          <t>248336; 308419</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>261470; 320983</t>
+          <t>262387; 320980</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172472; 220755</t>
+          <t>173321; 221758</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123137; 159298</t>
+          <t>123327; 158964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>398776; 465179</t>
+          <t>397033; 463049</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>493181; 568835</t>
+          <t>496352; 569776</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>351446; 416848</t>
+          <t>351995; 418077</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>272733; 316786</t>
+          <t>274644; 316576</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>666079; 756787</t>
+          <t>664875; 752621</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>778259; 876591</t>
+          <t>774411; 873842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>543277; 623150</t>
+          <t>544710; 622898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>409406; 466284</t>
+          <t>405065; 463790</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>217485; 279147</t>
+          <t>220603; 279499</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>374497; 448089</t>
+          <t>373510; 445839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>321547; 390872</t>
+          <t>325245; 394070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>253798; 422309</t>
+          <t>252404; 426905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>329270; 394601</t>
+          <t>332221; 398073</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>493370; 570787</t>
+          <t>492373; 574047</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>413050; 487893</t>
+          <t>416332; 492101</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>498251; 1109636</t>
+          <t>503550; 1105347</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>566086; 656310</t>
+          <t>563412; 654068</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>881911; 989941</t>
+          <t>884212; 994018</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>757817; 861777</t>
+          <t>756741; 857813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>826810; 1587829</t>
+          <t>841011; 1663904</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67267; 101454</t>
+          <t>68451; 104107</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47147; 78772</t>
+          <t>47403; 81641</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67473; 102944</t>
+          <t>68540; 104954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105841; 154174</t>
+          <t>105665; 158954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85104; 121412</t>
+          <t>87329; 123184</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77891; 115665</t>
+          <t>78133; 114467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89977; 127833</t>
+          <t>92457; 129306</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>138747; 176259</t>
+          <t>135953; 174573</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164615; 216566</t>
+          <t>161675; 212846</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132249; 183040</t>
+          <t>131933; 180647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>167326; 222951</t>
+          <t>169809; 219379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>251549; 313387</t>
+          <t>251187; 314116</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>567515; 656212</t>
+          <t>570263; 662516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>706802; 814552</t>
+          <t>713591; 808296</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>593074; 683772</t>
+          <t>589727; 680803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>484412; 697826</t>
+          <t>502703; 701798</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>841377; 950929</t>
+          <t>846053; 947894</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1104075; 1216226</t>
+          <t>1107804; 1218321</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>894366; 996855</t>
+          <t>893884; 1002706</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>956133; 1709159</t>
+          <t>962254; 1580570</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1444252; 1579259</t>
+          <t>1446647; 1569483</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1834592; 1999486</t>
+          <t>1851098; 2000397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1510508; 1658548</t>
+          <t>1510140; 1655647</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1550992; 2300462</t>
+          <t>1543718; 2406317</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 29,89</t>
+          <t>24,4; 30,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,92; 32,93</t>
+          <t>26,73; 32,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 29,4</t>
+          <t>23,35; 29,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 31,15</t>
+          <t>23,25; 30,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,19; 35,21</t>
+          <t>30,22; 35,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,1; 42,59</t>
+          <t>37,53; 42,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,39; 42,03</t>
+          <t>35,7; 41,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,84; 42,46</t>
+          <t>36,74; 42,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 32,07</t>
+          <t>28,23; 32,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,49; 37,79</t>
+          <t>33,47; 37,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,14; 35,61</t>
+          <t>30,91; 35,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,25; 36,93</t>
+          <t>32,05; 36,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,03; 16,51</t>
+          <t>12,95; 16,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 22,7</t>
+          <t>18,95; 22,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 18,98</t>
+          <t>15,61; 18,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 18,71</t>
+          <t>16,43; 20,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,93; 25,07</t>
+          <t>20,79; 25,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 32,66</t>
+          <t>27,88; 32,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,94; 24,75</t>
+          <t>20,65; 24,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,56; 49,52</t>
+          <t>23,06; 26,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 19,93</t>
+          <t>17,24; 20,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,76; 26,71</t>
+          <t>23,83; 26,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 21,1</t>
+          <t>18,65; 21,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,63; 36,86</t>
+          <t>20,13; 22,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 18,88</t>
+          <t>12,45; 18,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 16,97</t>
+          <t>9,85; 16,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 19,19</t>
+          <t>12,39; 18,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,4; 24,66</t>
+          <t>15,7; 21,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 25,86</t>
+          <t>18,24; 26,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 24,96</t>
+          <t>16,88; 24,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 23,55</t>
+          <t>16,79; 23,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,67; 26,55</t>
+          <t>21,6; 26,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 20,71</t>
+          <t>16,09; 21,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,04; 19,22</t>
+          <t>14,26; 19,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 20,02</t>
+          <t>15,42; 20,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,12</t>
+          <t>19,23; 23,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 20,22</t>
+          <t>17,28; 19,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 23,64</t>
+          <t>20,75; 23,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 20,16</t>
+          <t>17,61; 20,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 20,42</t>
+          <t>18,39; 21,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,05</t>
+          <t>25,04; 27,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,17; 34,28</t>
+          <t>30,93; 34,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,31; 28,39</t>
+          <t>25,29; 28,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,47; 43,48</t>
+          <t>26,54; 29,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,58</t>
+          <t>21,66; 23,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,54; 28,68</t>
+          <t>26,44; 28,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,86; 23,96</t>
+          <t>21,98; 23,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,83; 34,03</t>
+          <t>22,92; 24,78</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140917</t>
+          <t>151513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>294454</t>
+          <t>320879</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>435370</t>
+          <t>472392</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>248336; 308419</t>
+          <t>251759; 309768</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>262387; 320980</t>
+          <t>260546; 317691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173321; 221758</t>
+          <t>176157; 221946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123327; 158964</t>
+          <t>133370; 172324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>397033; 463049</t>
+          <t>397483; 465087</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>496352; 569776</t>
+          <t>502104; 571477</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>351995; 418077</t>
+          <t>355069; 415624</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>274644; 316576</t>
+          <t>298102; 341580</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>664875; 752621</t>
+          <t>662394; 753629</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>774411; 873842</t>
+          <t>773898; 869997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>544710; 622898</t>
+          <t>540628; 623839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>405065; 463790</t>
+          <t>443896; 500994</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362967</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>675263</t>
+          <t>534017</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1038230</t>
+          <t>938421</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>220603; 279499</t>
+          <t>219251; 276572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>373510; 445839</t>
+          <t>372075; 445946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>325245; 394070</t>
+          <t>324142; 391728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>252404; 426905</t>
+          <t>364985; 444640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>332221; 398073</t>
+          <t>330078; 400513</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>492373; 574047</t>
+          <t>490086; 568192</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>416332; 492101</t>
+          <t>410570; 487102</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>503550; 1105347</t>
+          <t>499300; 574290</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>563412; 654068</t>
+          <t>565637; 656515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>884212; 994018</t>
+          <t>886886; 1000358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>756741; 857813</t>
+          <t>758025; 864915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>841011; 1663904</t>
+          <t>883130; 991606</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126309</t>
+          <t>131816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>155280</t>
+          <t>175529</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>281589</t>
+          <t>307345</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68451; 104107</t>
+          <t>68673; 102556</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47403; 81641</t>
+          <t>47376; 79255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68540; 104954</t>
+          <t>67756; 103322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105665; 158954</t>
+          <t>111352; 154992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87329; 123184</t>
+          <t>86904; 124909</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78133; 114467</t>
+          <t>77408; 112922</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92457; 129306</t>
+          <t>92176; 129840</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>135953; 174573</t>
+          <t>158066; 196128</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161675; 212846</t>
+          <t>165357; 220549</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>131933; 180647</t>
+          <t>133971; 183337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>169809; 219379</t>
+          <t>169008; 221253</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>251187; 314116</t>
+          <t>277120; 337388</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>630193</t>
+          <t>687732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1124997</t>
+          <t>1030426</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1755189</t>
+          <t>1718158</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>570263; 662516</t>
+          <t>566182; 653942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>713591; 808296</t>
+          <t>709609; 811204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>589727; 680803</t>
+          <t>594947; 682194</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>502703; 701798</t>
+          <t>644460; 740242</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>846053; 947894</t>
+          <t>846234; 944763</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1107804; 1218321</t>
+          <t>1099379; 1214834</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>893884; 1002706</t>
+          <t>893106; 1000121</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>962254; 1580570</t>
+          <t>984460; 1079058</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1446647; 1569483</t>
+          <t>1441934; 1573020</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1851098; 2000397</t>
+          <t>1843959; 2000238</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1510140; 1655647</t>
+          <t>1518716; 1654743</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1543718; 2406317</t>
+          <t>1653159; 1787059</t>
         </is>
       </c>
     </row>
